--- a/ВОР.xlsx
+++ b/ВОР.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="120" windowWidth="16665" windowHeight="5865"/>
+    <workbookView xWindow="480" yWindow="120" windowWidth="16665" windowHeight="8130" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Пример" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="37">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -64,13 +64,76 @@
   </si>
   <si>
     <t>Монтаж углавого профиля</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Вид 1</t>
+  </si>
+  <si>
+    <t>Вид 2</t>
+  </si>
+  <si>
+    <t>Вид 3</t>
+  </si>
+  <si>
+    <t>Вид 4</t>
+  </si>
+  <si>
+    <t>Вид 5, 6 , 7 , 8</t>
+  </si>
+  <si>
+    <t>Итог</t>
+  </si>
+  <si>
+    <t>522.34 п.м.</t>
+  </si>
+  <si>
+    <t>15.16 п.м.</t>
+  </si>
+  <si>
+    <t>252.11 п.м.</t>
+  </si>
+  <si>
+    <t>71.89 п.м.</t>
+  </si>
+  <si>
+    <t>114.34 п.м.</t>
+  </si>
+  <si>
+    <t>68.84 п.м.</t>
+  </si>
+  <si>
+    <t>Объем, м²</t>
+  </si>
+  <si>
+    <t>Шпаклевка финишная</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </t>
+  </si>
+  <si>
+    <t>Объем, кг*</t>
+  </si>
+  <si>
+    <t>Окраска поверхности стен с предварительной огрунтовкой в 2 слоя:</t>
+  </si>
+  <si>
+    <t>Грунтовка универсальная</t>
+  </si>
+  <si>
+    <t>Матовая водно-дисперсионная краска RAL 9003 НГ</t>
+  </si>
+  <si>
+    <t>Монтаж углового профиля</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +141,21 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -160,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -183,6 +261,82 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -485,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D18"/>
+  <dimension ref="A2:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -494,14 +648,14 @@
     <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" s="5"/>
       <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
@@ -512,7 +666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -521,7 +675,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>2</v>
       </c>
@@ -530,7 +684,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>3</v>
       </c>
@@ -539,7 +693,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>4</v>
       </c>
@@ -548,7 +702,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>5</v>
       </c>
@@ -557,7 +711,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>6</v>
       </c>
@@ -566,7 +720,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>7</v>
       </c>
@@ -575,19 +729,24 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="12" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
       <c r="C14" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -598,7 +757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" s="2">
         <v>1</v>
       </c>
@@ -633,97 +792,633 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A4:E69"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="56.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="22"/>
+    <col min="3" max="3" width="59.5703125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+      <c r="D4" s="12"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="15">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="17"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B7" s="15">
+        <v>2</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="17"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B8" s="15">
+        <v>3</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="17"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="15">
+        <v>4</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="17"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B10" s="15">
+        <v>5</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="17"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B11" s="15">
+        <v>6</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="17"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B12" s="15">
+        <v>7</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="17"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="10"/>
+      <c r="C15" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="15">
+        <v>1</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="17">
+        <v>178.11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="15">
+        <v>2</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="15">
+        <v>3</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="17">
+        <v>178.11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="15">
+        <v>4</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="15">
+        <v>5</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="17">
+        <f>D17</f>
+        <v>178.11</v>
+      </c>
+      <c r="E21" s="13">
+        <v>9003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B24" s="10"/>
+      <c r="C24" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="15">
+        <v>1</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="17">
+        <v>340.88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="15">
+        <v>2</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B28" s="15">
+        <v>3</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="17">
+        <f>D26</f>
+        <v>340.88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B29" s="15">
+        <v>4</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B30" s="15">
+        <v>5</v>
+      </c>
+      <c r="C30" s="23" t="str">
+        <f>C21</f>
+        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
+      </c>
+      <c r="D30" s="17">
+        <f>D26</f>
+        <v>340.88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B33" s="10"/>
+      <c r="C33" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="12"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B34" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B35" s="15">
+        <v>1</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="17">
+        <v>192.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B36" s="15">
+        <v>2</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B37" s="15">
+        <v>3</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="17">
+        <f>D35</f>
+        <v>192.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B38" s="15">
+        <v>4</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B39" s="15">
+        <v>5</v>
+      </c>
+      <c r="C39" s="23" t="str">
+        <f>C30</f>
+        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
+      </c>
+      <c r="D39" s="17">
+        <f>D35</f>
+        <v>192.99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B40" s="19"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="21"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B43" s="10"/>
+      <c r="C43" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="12"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B44" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="17" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B45" s="15">
         <v>1</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C45" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="17">
+        <v>246.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B46" s="15">
+        <v>2</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="17">
         <v>0</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B47" s="15">
+        <v>3</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="17">
+        <f>D45</f>
+        <v>246.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B48" s="15">
+        <v>4</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B49" s="15">
+        <v>5</v>
+      </c>
+      <c r="C49" s="23" t="str">
+        <f>C39</f>
+        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
+      </c>
+      <c r="D49" s="17">
+        <f>D45</f>
+        <v>246.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B52" s="10"/>
+      <c r="C52" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="12"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B53" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B54" s="15">
+        <v>1</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="17">
+        <v>105.63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B55" s="15">
         <v>2</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C55" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="17">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B56" s="15">
+        <v>3</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" s="17">
+        <f>D54+D55</f>
+        <v>109.78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B57" s="15">
+        <v>4</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="25"/>
+      <c r="B58" s="26">
+        <v>5</v>
+      </c>
+      <c r="C58" s="23" t="str">
+        <f>C49</f>
+        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
+      </c>
+      <c r="D58" s="27">
+        <f>D54+D55</f>
+        <v>109.78</v>
+      </c>
+      <c r="E58" s="28"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B61" s="10"/>
+      <c r="C61" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="31"/>
+      <c r="E61" s="32"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B62" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B63" s="15">
         <v>1</v>
       </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
+      <c r="C63" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="17">
+        <v>1063.9100000000001</v>
+      </c>
+      <c r="E63" s="33"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B64" s="15">
+        <v>2</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="17">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E64" s="33"/>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B65" s="15">
         <v>3</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
+      <c r="C65" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" s="17">
+        <f>D63+D64</f>
+        <v>1068.0600000000002</v>
+      </c>
+      <c r="E65" s="33"/>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B66" s="15">
         <v>4</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="2">
+      <c r="C66" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="33"/>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B67" s="34">
         <v>5</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="2">
-        <v>7</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="2"/>
+      <c r="C67" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" s="17">
+        <f>D63+D64</f>
+        <v>1068.0600000000002</v>
+      </c>
+      <c r="E67" s="33"/>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B68" s="34">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="33"/>
+      <c r="E68" s="33">
+        <f>D67*0.15</f>
+        <v>160.20900000000003</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B69" s="34">
+        <v>5.2</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D69" s="33"/>
+      <c r="E69" s="33">
+        <f>D67*0.3</f>
+        <v>320.41800000000006</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ВОР.xlsx
+++ b/ВОР.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="38">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -108,9 +108,6 @@
     <t>Объем, м²</t>
   </si>
   <si>
-    <t>Шпаклевка финишная</t>
-  </si>
-  <si>
     <t xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </t>
   </si>
   <si>
@@ -127,6 +124,12 @@
   </si>
   <si>
     <t>Монтаж углового профиля</t>
+  </si>
+  <si>
+    <t>Шпаклевка финишная по ГВЛ</t>
+  </si>
+  <si>
+    <t>Шпаклевка финишная по оштукатуренной поверхности</t>
   </si>
 </sst>
 </file>
@@ -311,9 +314,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -337,6 +337,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -792,7 +795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:E69"/>
+  <dimension ref="A4:E75"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="9" customWidth="1"/>
@@ -942,11 +945,12 @@
         <v>3</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D19" s="17">
         <v>178.11</v>
       </c>
+      <c r="E19" s="34"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B20" s="15">
@@ -955,468 +959,536 @@
       <c r="C20" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>28</v>
-      </c>
+      <c r="D20" s="17">
+        <v>0</v>
+      </c>
+      <c r="E20" s="34"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" s="15">
         <v>5</v>
       </c>
-      <c r="C21" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="17">
+      <c r="C21" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B22" s="15">
+        <v>6</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="17">
         <f>D17</f>
         <v>178.11</v>
       </c>
-      <c r="E21" s="13">
-        <v>9003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B24" s="10"/>
-      <c r="C24" s="11" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="10"/>
+      <c r="C25" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="12"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B25" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="D25" s="12"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D26" s="17" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B26" s="15">
-        <v>1</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="17">
-        <v>340.88</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D27" s="17">
-        <v>0</v>
+        <v>340.88</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D28" s="17">
-        <f>D26</f>
-        <v>340.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B29" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>27</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D29" s="17">
+        <v>340.88</v>
+      </c>
+      <c r="E29" s="34"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B30" s="15">
+        <v>4</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="17">
+        <v>0</v>
+      </c>
+      <c r="E30" s="34"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B31" s="15">
         <v>5</v>
       </c>
-      <c r="C30" s="23" t="str">
-        <f>C21</f>
+      <c r="C31" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B32" s="15">
+        <v>6</v>
+      </c>
+      <c r="C32" s="23" t="str">
+        <f>C22</f>
         <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
       </c>
-      <c r="D30" s="17">
-        <f>D26</f>
+      <c r="D32" s="17">
+        <f>D27</f>
         <v>340.88</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="10"/>
-      <c r="C33" s="11" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="10"/>
+      <c r="C35" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="12"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B34" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="D35" s="12"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D36" s="17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B35" s="15">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="15">
         <v>1</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C37" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D37" s="17">
         <v>192.99</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="15">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B38" s="15">
         <v>2</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C38" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D38" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="15">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B39" s="15">
         <v>3</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="17">
-        <f>D35</f>
+      <c r="C39" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="17">
         <v>192.99</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B38" s="15">
+      <c r="E39" s="34"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="15">
         <v>4</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C40" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D40" s="17">
+        <v>0</v>
+      </c>
+      <c r="E40" s="34"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B41" s="15">
+        <v>5</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="17" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B39" s="15">
-        <v>5</v>
-      </c>
-      <c r="C39" s="23" t="str">
-        <f>C30</f>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="15">
+        <v>6</v>
+      </c>
+      <c r="C42" s="23" t="str">
+        <f>C32</f>
         <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
       </c>
-      <c r="D39" s="17">
-        <f>D35</f>
+      <c r="D42" s="17">
+        <f>D37</f>
         <v>192.99</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B40" s="19"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="21"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="9" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="19"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="21"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B43" s="10"/>
-      <c r="C43" s="11" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B46" s="10"/>
+      <c r="C46" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="12"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B44" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="16" t="s">
+      <c r="D46" s="12"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B47" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D47" s="17" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B45" s="15">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B48" s="15">
         <v>1</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C48" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D48" s="17">
         <v>246.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B46" s="15">
-        <v>2</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B47" s="15">
-        <v>3</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="17">
-        <f>D45</f>
-        <v>246.3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B48" s="15">
-        <v>4</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B49" s="15">
+        <v>2</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B50" s="15">
+        <v>3</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" s="17">
+        <v>246.3</v>
+      </c>
+      <c r="E50" s="34"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B51" s="15">
+        <v>4</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="17">
+        <v>0</v>
+      </c>
+      <c r="E51" s="34"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B52" s="15">
         <v>5</v>
       </c>
-      <c r="C49" s="23" t="str">
-        <f>C39</f>
+      <c r="C52" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B53" s="15">
+        <v>6</v>
+      </c>
+      <c r="C53" s="23" t="str">
+        <f>C42</f>
         <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
       </c>
-      <c r="D49" s="17">
-        <f>D45</f>
+      <c r="D53" s="17">
+        <f>D48</f>
         <v>246.3</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="9" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B52" s="10"/>
-      <c r="C52" s="11" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B56" s="10"/>
+      <c r="C56" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="12"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B53" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="16" t="s">
+      <c r="D56" s="12"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B57" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D57" s="17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B54" s="15">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B58" s="15">
         <v>1</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C58" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="17">
+      <c r="D58" s="17">
         <v>105.63</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B55" s="15">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B59" s="15">
         <v>2</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C59" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="17">
+      <c r="D59" s="17">
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B56" s="15">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B60" s="15">
         <v>3</v>
       </c>
-      <c r="C56" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D56" s="17">
-        <f>D54+D55</f>
+      <c r="C60" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D60" s="17">
+        <v>105.63</v>
+      </c>
+      <c r="E60" s="34"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B61" s="15">
+        <v>4</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" s="17">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E61" s="34"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B62" s="15">
+        <v>5</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="25"/>
+      <c r="B63" s="15">
+        <v>6</v>
+      </c>
+      <c r="C63" s="23" t="str">
+        <f>C53</f>
+        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
+      </c>
+      <c r="D63" s="26">
+        <f>D58+D59</f>
         <v>109.78</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B57" s="15">
+      <c r="E63" s="27"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B66" s="10"/>
+      <c r="C66" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="30"/>
+      <c r="E66" s="31"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B67" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B68" s="15">
+        <v>1</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="17">
+        <v>1063.9100000000001</v>
+      </c>
+      <c r="E68" s="32"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B69" s="15">
+        <v>2</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="17">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E69" s="32"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B70" s="15">
+        <v>3</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" s="17">
+        <v>1063.9100000000001</v>
+      </c>
+      <c r="E70" s="32"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B71" s="15">
         <v>4</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C71" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="25"/>
-      <c r="B58" s="26">
+      <c r="D71" s="17">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E71" s="32"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B72" s="15">
         <v>5</v>
       </c>
-      <c r="C58" s="23" t="str">
-        <f>C49</f>
-        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
-      </c>
-      <c r="D58" s="27">
-        <f>D54+D55</f>
-        <v>109.78</v>
-      </c>
-      <c r="E58" s="28"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B61" s="10"/>
-      <c r="C61" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="31"/>
-      <c r="E61" s="32"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B62" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E62" s="33" t="s">
+      <c r="C72" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" s="32"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B73" s="15">
+        <v>6</v>
+      </c>
+      <c r="C73" s="23" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B63" s="15">
-        <v>1</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" s="17">
-        <v>1063.9100000000001</v>
-      </c>
-      <c r="E63" s="33"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B64" s="15">
-        <v>2</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D64" s="17">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="E64" s="33"/>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B65" s="15">
-        <v>3</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D65" s="17">
-        <f>D63+D64</f>
+      <c r="D73" s="17">
+        <f>D68+D69</f>
         <v>1068.0600000000002</v>
       </c>
-      <c r="E65" s="33"/>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B66" s="15">
-        <v>4</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E66" s="33"/>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B67" s="34">
-        <v>5</v>
-      </c>
-      <c r="C67" s="23" t="s">
+      <c r="E73" s="32"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B74" s="33">
+        <v>6.1</v>
+      </c>
+      <c r="C74" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D67" s="17">
-        <f>D63+D64</f>
-        <v>1068.0600000000002</v>
-      </c>
-      <c r="E67" s="33"/>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B68" s="34">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="C68" s="16" t="s">
+      <c r="D74" s="32"/>
+      <c r="E74" s="32">
+        <f>D73*0.15</f>
+        <v>160.20900000000003</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B75" s="33">
+        <v>6.2</v>
+      </c>
+      <c r="C75" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D68" s="33"/>
-      <c r="E68" s="33">
-        <f>D67*0.15</f>
-        <v>160.20900000000003</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B69" s="34">
-        <v>5.2</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D69" s="33"/>
-      <c r="E69" s="33">
-        <f>D67*0.3</f>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32">
+        <f>D73*0.3</f>
         <v>320.41800000000006</v>
       </c>
     </row>

--- a/ВОР.xlsx
+++ b/ВОР.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="120" windowWidth="16665" windowHeight="8130" activeTab="1"/>
+    <workbookView xWindow="23265" yWindow="5565" windowWidth="16665" windowHeight="8130" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Пример" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621" refMode="R1C1"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="45">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -130,6 +130,27 @@
   </si>
   <si>
     <t>Шпаклевка финишная по оштукатуренной поверхности</t>
+  </si>
+  <si>
+    <t>Зашивка коммуникации ГВЛ в 1 слой</t>
+  </si>
+  <si>
+    <t>итог</t>
+  </si>
+  <si>
+    <t>16.00 п.м.</t>
+  </si>
+  <si>
+    <t>Откосы</t>
+  </si>
+  <si>
+    <t>Шпаклевка оконных откосов базовая</t>
+  </si>
+  <si>
+    <t>Шпаклевка оконных откосов финишная</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Окраска поверхности откосов с предварительной огрунтовкой в 2 слоя </t>
   </si>
 </sst>
 </file>
@@ -169,7 +190,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -237,11 +258,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -339,6 +382,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -795,7 +844,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:E75"/>
+  <dimension ref="A4:E96"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="9" customWidth="1"/>
@@ -1492,6 +1541,169 @@
         <v>320.41800000000006</v>
       </c>
     </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B78" s="10"/>
+      <c r="C78" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="35"/>
+      <c r="E78" s="36"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B79" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B80" s="15">
+        <v>1</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80" s="17">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" s="10"/>
+      <c r="C84" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="12"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B85" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B86" s="15">
+        <v>1</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D86" s="17">
+        <v>28.72</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B87" s="15">
+        <v>2</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" s="10"/>
+      <c r="C90" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="12"/>
+      <c r="E90" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B91" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E91" s="32"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B92" s="15">
+        <v>1</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="17">
+        <v>37.68</v>
+      </c>
+      <c r="E92" s="32"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B93" s="15">
+        <v>2</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D93" s="17">
+        <f>D92</f>
+        <v>37.68</v>
+      </c>
+      <c r="E93" s="32"/>
+    </row>
+    <row r="94" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="25"/>
+      <c r="B94" s="15">
+        <v>3</v>
+      </c>
+      <c r="C94" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D94" s="26">
+        <f>D92</f>
+        <v>37.68</v>
+      </c>
+      <c r="E94" s="32"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B95" s="33">
+        <v>3.1</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" s="32"/>
+      <c r="E95" s="32">
+        <f>D92*0.15</f>
+        <v>5.6520000000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B96" s="33">
+        <v>3.2</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" s="32"/>
+      <c r="E96" s="32">
+        <f>D92*0.3</f>
+        <v>11.304</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ВОР.xlsx
+++ b/ВОР.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="23265" yWindow="5565" windowWidth="16665" windowHeight="8130" activeTab="1"/>
+    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Пример" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="46">
   <si>
     <t>Штукатурка цементным составом толщиной 16‐20 мм</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t xml:space="preserve">Окраска поверхности откосов с предварительной огрунтовкой в 2 слоя </t>
+  </si>
+  <si>
+    <t>332 п.м</t>
   </si>
 </sst>
 </file>
@@ -844,7 +847,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:E96"/>
+  <dimension ref="A4:E92"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="9" customWidth="1"/>
@@ -855,7 +858,7 @@
     <col min="6" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
@@ -865,7 +868,7 @@
       </c>
       <c r="D4" s="12"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
@@ -876,831 +879,802 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B6" s="15">
         <v>1</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="17"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="17">
+        <v>2943.23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B7" s="15">
         <v>2</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="17"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="D7" s="17">
+        <f>D6</f>
+        <v>2943.23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B8" s="15">
         <v>3</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="10"/>
+      <c r="C11" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="12"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="15">
+        <v>1</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="17">
+        <v>178.11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="15">
         <v>2</v>
       </c>
-      <c r="D8" s="17"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B9" s="15">
+      <c r="C14" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="15">
+        <v>3</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="17">
+        <v>178.11</v>
+      </c>
+      <c r="E15" s="34"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="15">
         <v>4</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="17"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B10" s="15">
-        <v>5</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="17"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B11" s="15">
-        <v>6</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="17"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B12" s="15">
-        <v>7</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="17"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="19"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="21"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="10"/>
-      <c r="C15" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="12"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="15" t="s">
-        <v>6</v>
-      </c>
       <c r="C16" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>29</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0</v>
+      </c>
+      <c r="E16" s="34"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B17" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="17">
-        <v>178.11</v>
+        <v>35</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B18" s="15">
+        <v>6</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="17">
+        <f>D13</f>
+        <v>178.11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="10"/>
+      <c r="C21" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="12"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B22" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="15">
+        <v>1</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="17">
+        <v>340.88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B24" s="15">
         <v>2</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C24" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D24" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="15">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="15">
         <v>3</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C25" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="17">
-        <v>178.11</v>
-      </c>
-      <c r="E19" s="34"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B20" s="15">
+      <c r="D25" s="17">
+        <v>340.88</v>
+      </c>
+      <c r="E25" s="34"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="15">
         <v>4</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C26" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D26" s="17">
         <v>0</v>
       </c>
-      <c r="E20" s="34"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B21" s="15">
-        <v>5</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B22" s="15">
-        <v>6</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="17">
-        <f>D17</f>
-        <v>178.11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B25" s="10"/>
-      <c r="C25" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="12"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B26" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>29</v>
-      </c>
+      <c r="E26" s="34"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B27" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="17">
-        <v>340.88</v>
+        <v>35</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B28" s="15">
+        <v>6</v>
+      </c>
+      <c r="C28" s="23" t="str">
+        <f>C18</f>
+        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
+      </c>
+      <c r="D28" s="17">
+        <f>D23</f>
+        <v>340.88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B31" s="10"/>
+      <c r="C31" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="12"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B32" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B33" s="15">
+        <v>1</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="17">
+        <v>192.99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B34" s="15">
         <v>2</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C34" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D34" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B29" s="15">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="15">
         <v>3</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C35" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="17">
-        <v>340.88</v>
-      </c>
-      <c r="E29" s="34"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B30" s="15">
+      <c r="D35" s="17">
+        <v>192.99</v>
+      </c>
+      <c r="E35" s="34"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="15">
         <v>4</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C36" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D36" s="17">
         <v>0</v>
       </c>
-      <c r="E30" s="34"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B31" s="15">
-        <v>5</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B32" s="15">
-        <v>6</v>
-      </c>
-      <c r="C32" s="23" t="str">
-        <f>C22</f>
-        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
-      </c>
-      <c r="D32" s="17">
-        <f>D27</f>
-        <v>340.88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B35" s="10"/>
-      <c r="C35" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="12"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B36" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>29</v>
-      </c>
+      <c r="E36" s="34"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B37" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="17">
-        <v>192.99</v>
+        <v>35</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B38" s="15">
+        <v>6</v>
+      </c>
+      <c r="C38" s="23" t="str">
+        <f>C28</f>
+        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
+      </c>
+      <c r="D38" s="17">
+        <f>D33</f>
+        <v>192.99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B39" s="19"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="21"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="10"/>
+      <c r="C42" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="12"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B44" s="15">
+        <v>1</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="17">
+        <v>246.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B45" s="15">
         <v>2</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C45" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D38" s="17">
+      <c r="D45" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B39" s="15">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B46" s="15">
         <v>3</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C46" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="17">
-        <v>192.99</v>
-      </c>
-      <c r="E39" s="34"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B40" s="15">
+      <c r="D46" s="17">
+        <v>246.3</v>
+      </c>
+      <c r="E46" s="34"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B47" s="15">
         <v>4</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C47" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D47" s="17">
         <v>0</v>
       </c>
-      <c r="E40" s="34"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B41" s="15">
-        <v>5</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B42" s="15">
-        <v>6</v>
-      </c>
-      <c r="C42" s="23" t="str">
-        <f>C32</f>
-        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
-      </c>
-      <c r="D42" s="17">
-        <f>D37</f>
-        <v>192.99</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B43" s="19"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="21"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B46" s="10"/>
-      <c r="C46" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="12"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B47" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>8</v>
-      </c>
+      <c r="E47" s="34"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B48" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="17">
-        <v>246.3</v>
+        <v>35</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B49" s="15">
+        <v>6</v>
+      </c>
+      <c r="C49" s="23" t="str">
+        <f>C38</f>
+        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
+      </c>
+      <c r="D49" s="17">
+        <f>D44</f>
+        <v>246.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B52" s="10"/>
+      <c r="C52" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="12"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B53" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B54" s="15">
+        <v>1</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="17">
+        <v>105.63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B55" s="15">
         <v>2</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C55" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D49" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B50" s="15">
+      <c r="D55" s="17">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B56" s="15">
         <v>3</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C56" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D50" s="17">
-        <v>246.3</v>
-      </c>
-      <c r="E50" s="34"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B51" s="15">
+      <c r="D56" s="17">
+        <v>105.63</v>
+      </c>
+      <c r="E56" s="34"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B57" s="15">
         <v>4</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C57" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="17">
-        <v>0</v>
-      </c>
-      <c r="E51" s="34"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B52" s="15">
-        <v>5</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B53" s="15">
-        <v>6</v>
-      </c>
-      <c r="C53" s="23" t="str">
-        <f>C42</f>
-        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
-      </c>
-      <c r="D53" s="17">
-        <f>D48</f>
-        <v>246.3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B56" s="10"/>
-      <c r="C56" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="12"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B57" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="17" t="s">
-        <v>29</v>
-      </c>
+      <c r="D57" s="17">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="E57" s="34"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B58" s="15">
+        <v>5</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="25"/>
+      <c r="B59" s="15">
+        <v>6</v>
+      </c>
+      <c r="C59" s="23" t="str">
+        <f>C49</f>
+        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
+      </c>
+      <c r="D59" s="26">
+        <f>D54+D55</f>
+        <v>109.78</v>
+      </c>
+      <c r="E59" s="27"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B62" s="10"/>
+      <c r="C62" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="30"/>
+      <c r="E62" s="31"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B63" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B64" s="15">
         <v>1</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C64" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D58" s="17">
-        <v>105.63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B59" s="15">
+      <c r="D64" s="17">
+        <v>1063.9100000000001</v>
+      </c>
+      <c r="E64" s="32"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B65" s="15">
         <v>2</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C65" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D59" s="17">
+      <c r="D65" s="17">
         <v>4.1500000000000004</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B60" s="15">
+      <c r="E65" s="32"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B66" s="15">
         <v>3</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C66" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D60" s="17">
-        <v>105.63</v>
-      </c>
-      <c r="E60" s="34"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B61" s="15">
+      <c r="D66" s="17">
+        <v>1063.9100000000001</v>
+      </c>
+      <c r="E66" s="32"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B67" s="15">
         <v>4</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C67" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D61" s="17">
+      <c r="D67" s="17">
         <v>4.1500000000000004</v>
       </c>
-      <c r="E61" s="34"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B62" s="15">
-        <v>5</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="25"/>
-      <c r="B63" s="15">
-        <v>6</v>
-      </c>
-      <c r="C63" s="23" t="str">
-        <f>C53</f>
-        <v xml:space="preserve">Окраска поверхности стен с предварительной огрунтовкой в 2 слоя </v>
-      </c>
-      <c r="D63" s="26">
-        <f>D58+D59</f>
-        <v>109.78</v>
-      </c>
-      <c r="E63" s="27"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B66" s="10"/>
-      <c r="C66" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="30"/>
-      <c r="E66" s="31"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B67" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E67" s="32" t="s">
-        <v>31</v>
-      </c>
+      <c r="E67" s="32"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B68" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="17">
-        <v>1063.9100000000001</v>
+        <v>35</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E68" s="32"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B69" s="15">
+        <v>6</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" s="17">
+        <f>D64+D65</f>
+        <v>1068.0600000000002</v>
+      </c>
+      <c r="E69" s="32"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B70" s="33">
+        <v>6.1</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32">
+        <f>D69*0.15</f>
+        <v>160.20900000000003</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B71" s="33">
+        <v>6.2</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32">
+        <f>D69*0.3</f>
+        <v>320.41800000000006</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B74" s="10"/>
+      <c r="C74" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="35"/>
+      <c r="E74" s="36"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B75" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B76" s="15">
+        <v>1</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D76" s="17">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80" s="10"/>
+      <c r="C80" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="12"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B81" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B82" s="15">
+        <v>1</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D82" s="17">
+        <v>28.72</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B83" s="15">
         <v>2</v>
       </c>
-      <c r="C69" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" s="17">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="E69" s="32"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B70" s="15">
+      <c r="C83" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B86" s="10"/>
+      <c r="C86" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" s="12"/>
+      <c r="E86" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B87" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="32"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B88" s="15">
+        <v>1</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D88" s="17">
+        <v>37.68</v>
+      </c>
+      <c r="E88" s="32"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B89" s="15">
+        <v>2</v>
+      </c>
+      <c r="C89" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D89" s="17">
+        <f>D88</f>
+        <v>37.68</v>
+      </c>
+      <c r="E89" s="32"/>
+    </row>
+    <row r="90" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="25"/>
+      <c r="B90" s="15">
         <v>3</v>
       </c>
-      <c r="C70" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D70" s="17">
-        <v>1063.9100000000001</v>
-      </c>
-      <c r="E70" s="32"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B71" s="15">
-        <v>4</v>
-      </c>
-      <c r="C71" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D71" s="17">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="E71" s="32"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B72" s="15">
-        <v>5</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D72" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E72" s="32"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B73" s="15">
-        <v>6</v>
-      </c>
-      <c r="C73" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D73" s="17">
-        <f>D68+D69</f>
-        <v>1068.0600000000002</v>
-      </c>
-      <c r="E73" s="32"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B74" s="33">
-        <v>6.1</v>
-      </c>
-      <c r="C74" s="16" t="s">
+      <c r="C90" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D90" s="26">
+        <f>D88</f>
+        <v>37.68</v>
+      </c>
+      <c r="E90" s="32"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B91" s="33">
+        <v>3.1</v>
+      </c>
+      <c r="C91" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D74" s="32"/>
-      <c r="E74" s="32">
-        <f>D73*0.15</f>
-        <v>160.20900000000003</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B75" s="33">
-        <v>6.2</v>
-      </c>
-      <c r="C75" s="16" t="s">
+      <c r="D91" s="32"/>
+      <c r="E91" s="32">
+        <f>D88*0.15</f>
+        <v>5.6520000000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B92" s="33">
+        <v>3.2</v>
+      </c>
+      <c r="C92" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32">
-        <f>D73*0.3</f>
-        <v>320.41800000000006</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B78" s="10"/>
-      <c r="C78" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D78" s="35"/>
-      <c r="E78" s="36"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B79" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D79" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B80" s="15">
-        <v>1</v>
-      </c>
-      <c r="C80" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D80" s="17">
-        <v>4.1500000000000004</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B84" s="10"/>
-      <c r="C84" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D84" s="12"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B85" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B86" s="15">
-        <v>1</v>
-      </c>
-      <c r="C86" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D86" s="17">
-        <v>28.72</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B87" s="15">
-        <v>2</v>
-      </c>
-      <c r="C87" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D87" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B90" s="10"/>
-      <c r="C90" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="12"/>
-      <c r="E90" s="32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B91" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E91" s="32"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B92" s="15">
-        <v>1</v>
-      </c>
-      <c r="C92" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D92" s="17">
-        <v>37.68</v>
-      </c>
-      <c r="E92" s="32"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B93" s="15">
-        <v>2</v>
-      </c>
-      <c r="C93" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D93" s="17">
-        <f>D92</f>
-        <v>37.68</v>
-      </c>
-      <c r="E93" s="32"/>
-    </row>
-    <row r="94" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="25"/>
-      <c r="B94" s="15">
-        <v>3</v>
-      </c>
-      <c r="C94" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D94" s="26">
-        <f>D92</f>
-        <v>37.68</v>
-      </c>
-      <c r="E94" s="32"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B95" s="33">
-        <v>3.1</v>
-      </c>
-      <c r="C95" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D95" s="32"/>
-      <c r="E95" s="32">
-        <f>D92*0.15</f>
-        <v>5.6520000000000001</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B96" s="33">
-        <v>3.2</v>
-      </c>
-      <c r="C96" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D96" s="32"/>
-      <c r="E96" s="32">
-        <f>D92*0.3</f>
+      <c r="D92" s="32"/>
+      <c r="E92" s="32">
+        <f>D88*0.3</f>
         <v>11.304</v>
       </c>
     </row>
